--- a/Hospital-Management-API/media/lab_pricing_templates/LabPricing_BR530DA223BE_v1.xlsx
+++ b/Hospital-Management-API/media/lab_pricing_templates/LabPricing_BR530DA223BE_v1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3341,24 +3341,28 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF7F6000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
